--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,27 +789,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108157112</v>
+        <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58602</v>
+        <v>58283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103019</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -866,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +906,378 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137077099</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137077170</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Holmtorpet Skogen, Lindö, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>573789</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6496245</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137077170</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137077094</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holmtorpet Skogen, Lindö, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6496245</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137077094</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108157112</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmtorpet Skogen, Lindö, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573789</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6496245</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Hjelte</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/108157112</t>
         </is>
@@ -915,6 +1287,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -824,11 +824,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -948,11 +944,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1072,11 +1064,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3815-2026 artfynd.xlsx
+++ b/artfynd/A 3815-2026 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>137077099</v>
       </c>
       <c r="B3" t="n">
-        <v>58310</v>
+        <v>58313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137077170</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>137077094</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
